--- a/website/examples/example_odk_scaled_photo.capture.xlsx
+++ b/website/examples/example_odk_scaled_photo.capture.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R9737419f99564f89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R7fe5704993ad4bf1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rd3ed42a63e224da1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rf1873aa9de144fcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R58db450dee6345d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R7ee97e8357934ef4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -296,7 +296,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="E2" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='scaled_photo.capture',input_ruler_length_mm='50',input_hud_scale_ratio='1',input_capture_orientation='portrait',input_grid_rows='10',input_grid_columns='10',input_show_grid='true',return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='scaled_photo.capture',input_ruler_length_mm='50',input_hud_scale_ratio='1',input_capture_orientation='portrait',input_grid_rows='10',input_grid_columns='10',input_show_grid='true',return_mode='flat')</x:v>
       </x:c>
       <x:c r="F2"/>
     </x:row>
@@ -305,10 +305,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>researchos_execution_id</x:v>
+        <x:v>methodmesh_execution_id</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>ResearchOS execution ID</x:v>
+        <x:v>MethodMesh execution ID</x:v>
       </x:c>
       <x:c r="D3"/>
       <x:c r="E3"/>
@@ -319,10 +319,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>researchos_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>ResearchOS status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D4"/>
       <x:c r="E4"/>
